--- a/final/table/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
+++ b/final/table/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
@@ -118,7 +118,7 @@
     <t xml:space="preserve">AbsEffect</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature</t>
+    <t xml:space="preserve">FoldChange</t>
   </si>
   <si>
     <t xml:space="preserve">Class_A</t>
@@ -184,112 +184,112 @@
     <t xml:space="preserve">significance</t>
   </si>
   <si>
+    <t xml:space="preserve">PS/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LI &gt; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">****</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQDG/TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LI &lt; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/DG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/LPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/DG</t>
+  </si>
+  <si>
     <t xml:space="preserve">MG/SQDG</t>
   </si>
   <si>
-    <t xml:space="preserve">LI &gt; C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***</t>
+    <t xml:space="preserve">TG/PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG/PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG/PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG/PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/DGDG</t>
   </si>
   <si>
     <t xml:space="preserve">MG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LI &lt; C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/DG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPE/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG/PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGDG/PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPE/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQDG/TG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/LPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGDG/PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/DG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/DGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/PE</t>
   </si>
   <si>
     <t xml:space="preserve">Rank</t>
@@ -1273,6 +1273,9 @@
       <c r="E1" t="s">
         <v>32</v>
       </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -1282,13 +1285,16 @@
         <v>1.01679180751706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.965384586884283</v>
+        <v>0.963345098556201</v>
       </c>
       <c r="D2" t="n">
-        <v>1.06819902814984</v>
+        <v>1.06783290688334</v>
       </c>
       <c r="E2" t="n">
         <v>1.01679180751706</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76431207767127</v>
       </c>
     </row>
     <row r="3">
@@ -1299,13 +1305,16 @@
         <v>-0.942084768792643</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.961683674129789</v>
+        <v>-0.960422158596724</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.922485863455497</v>
+        <v>-0.923003273268884</v>
       </c>
       <c r="E3" t="n">
         <v>0.942084768792643</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.389814314933473</v>
       </c>
     </row>
     <row r="4">
@@ -1316,13 +1325,16 @@
         <v>0.606787664895789</v>
       </c>
       <c r="C4" t="n">
-        <v>0.575546751659754</v>
+        <v>0.57643459802212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.638028578131824</v>
+        <v>0.636077378592577</v>
       </c>
       <c r="E4" t="n">
         <v>0.606787664895789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.83452880202761</v>
       </c>
     </row>
     <row r="5">
@@ -1333,13 +1345,16 @@
         <v>0.476795091624303</v>
       </c>
       <c r="C5" t="n">
-        <v>0.444203354906905</v>
+        <v>0.444514374205478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.509386828341701</v>
+        <v>0.507016311174211</v>
       </c>
       <c r="E5" t="n">
         <v>0.476795091624303</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.61090332264983</v>
       </c>
     </row>
     <row r="6">
@@ -1350,13 +1365,16 @@
         <v>-0.387697842178366</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.402149145041434</v>
+        <v>-0.400973681333276</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.373246539315298</v>
+        <v>-0.373329791362068</v>
       </c>
       <c r="E6" t="n">
         <v>0.387697842178366</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.678617361832337</v>
       </c>
     </row>
     <row r="7">
@@ -1364,16 +1382,19 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.257393836490202</v>
+        <v>-0.257393836490201</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.274896533696464</v>
+        <v>-0.273108899213287</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.239891139283939</v>
+        <v>-0.239853896338556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.257393836490202</v>
+        <v>0.257393836490201</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.773063693112115</v>
       </c>
     </row>
     <row r="8">
@@ -1384,13 +1405,16 @@
         <v>-0.217351018084144</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.242772892363539</v>
+        <v>-0.240708283740906</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.191929143804749</v>
+        <v>-0.192543403384832</v>
       </c>
       <c r="E8" t="n">
         <v>0.217351018084144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.804647473912702</v>
       </c>
     </row>
     <row r="9">
@@ -1401,13 +1425,16 @@
         <v>0.196534115908537</v>
       </c>
       <c r="C9" t="n">
-        <v>0.119863881003202</v>
+        <v>0.120264423197661</v>
       </c>
       <c r="D9" t="n">
-        <v>0.273204350813872</v>
+        <v>0.262478004623756</v>
       </c>
       <c r="E9" t="n">
         <v>0.196534115908537</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.21717684526379</v>
       </c>
     </row>
     <row r="10">
@@ -1418,13 +1445,16 @@
         <v>-0.164857820904893</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.17890481494529</v>
+        <v>-0.176975660017586</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.150810826864496</v>
+        <v>-0.150610465641452</v>
       </c>
       <c r="E10" t="n">
         <v>0.164857820904893</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.848014265417958</v>
       </c>
     </row>
     <row r="11">
@@ -1435,13 +1465,16 @@
         <v>-0.138396589272123</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.168313189623793</v>
+        <v>-0.165203860740266</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.108479988920452</v>
+        <v>-0.11049119128913</v>
       </c>
       <c r="E11" t="n">
         <v>0.138396589272123</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.870753291845166</v>
       </c>
     </row>
     <row r="12">
@@ -1452,13 +1485,16 @@
         <v>-0.113730552131991</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.12938081738697</v>
+        <v>-0.128339441748043</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0980802868770111</v>
+        <v>-0.0977038079204138</v>
       </c>
       <c r="E12" t="n">
         <v>0.113730552131991</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.892498405279169</v>
       </c>
     </row>
     <row r="13">
@@ -1469,13 +1505,16 @@
         <v>-0.0637052080233771</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0858449218838025</v>
+        <v>-0.0869272162166274</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0415654941629517</v>
+        <v>-0.0419363782991806</v>
       </c>
       <c r="E13" t="n">
         <v>0.0637052080233771</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.938281556640029</v>
       </c>
     </row>
     <row r="14">
@@ -1483,16 +1522,19 @@
         <v>24</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.011691044067951</v>
+        <v>-0.0116910440679509</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0271603445232908</v>
+        <v>-0.0261171994836666</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00377825638738887</v>
+        <v>0.00358719446786396</v>
       </c>
       <c r="E14" t="n">
-        <v>0.011691044067951</v>
+        <v>0.0116910440679509</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.98837703064135</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1550,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>29</v>
@@ -1520,10 +1562,10 @@
         <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -1534,16 +1576,16 @@
         <v>-1.41887986041695</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.45791140569514</v>
+        <v>-1.4548410584564</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.37984831513875</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
+        <v>-1.38043961352675</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.41887986041695</v>
       </c>
       <c r="F2" t="n">
-        <v>1.41887986041695</v>
+        <v>0.241984922032599</v>
       </c>
     </row>
     <row r="3">
@@ -1554,16 +1596,16 @@
         <v>-0.864492933802669</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.899844053989973</v>
+        <v>-0.896464567053855</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.829141813615366</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
+        <v>-0.829201288126029</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.864492933802669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.864492933802669</v>
+        <v>0.421265107775715</v>
       </c>
     </row>
     <row r="4">
@@ -1574,16 +1616,16 @@
         <v>-0.734188928114504</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.771121298494346</v>
+        <v>-0.768133830419512</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.697256557734663</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
+        <v>-0.696850694346989</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.734188928114504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.734188928114504</v>
+        <v>0.47989453013262</v>
       </c>
     </row>
     <row r="5">
@@ -1594,16 +1636,16 @@
         <v>-0.694146109708447</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.740059938203823</v>
+        <v>-0.735344685091511</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.648232281213071</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
+        <v>-0.649983897229075</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.694146109708447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.694146109708447</v>
+        <v>0.499500784807565</v>
       </c>
     </row>
     <row r="6">
@@ -1614,16 +1656,16 @@
         <v>-0.641652912529196</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.675790148044542</v>
+        <v>-0.672671815989876</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.60751567701385</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>-0.606450884643303</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.641652912529196</v>
       </c>
       <c r="F6" t="n">
-        <v>0.641652912529196</v>
+        <v>0.526421575705134</v>
       </c>
     </row>
     <row r="7">
@@ -1634,16 +1676,16 @@
         <v>-0.615191680896426</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.666165733750349</v>
+        <v>-0.661244145122262</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.564217628042503</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
+        <v>-0.566635759040863</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.615191680896426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.615191680896426</v>
+        <v>0.540537274709221</v>
       </c>
     </row>
     <row r="8">
@@ -1654,16 +1696,16 @@
         <v>-0.590525643756294</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.624870148604906</v>
+        <v>-0.621757626033544</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.556181138907683</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
+        <v>-0.555777566363953</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.590525643756294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.590525643756294</v>
+        <v>0.554035982625617</v>
       </c>
     </row>
     <row r="9">
@@ -1674,16 +1716,16 @@
         <v>-0.54050029964768</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.581175203167648</v>
+        <v>-0.577896949302591</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.499825396127712</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
+        <v>-0.49777145837224</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.54050029964768</v>
       </c>
       <c r="F9" t="n">
-        <v>0.54050029964768</v>
+        <v>0.582456776547347</v>
       </c>
     </row>
     <row r="10">
@@ -1694,16 +1736,16 @@
         <v>0.539996715892756</v>
       </c>
       <c r="C10" t="n">
-        <v>0.480104133629591</v>
+        <v>0.480657206539488</v>
       </c>
       <c r="D10" t="n">
-        <v>0.599889298155921</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
+        <v>0.597447522236217</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.539996715892756</v>
       </c>
       <c r="F10" t="n">
-        <v>0.539996715892756</v>
+        <v>1.71600122664355</v>
       </c>
     </row>
     <row r="11">
@@ -1714,16 +1756,16 @@
         <v>-0.488486135692254</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.527242731345236</v>
+        <v>-0.524684265083625</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.449729540039273</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
+        <v>-0.44656089467468</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.488486135692254</v>
       </c>
       <c r="F11" t="n">
-        <v>0.488486135692254</v>
+        <v>0.613554529774969</v>
       </c>
     </row>
     <row r="12">
@@ -1734,16 +1776,16 @@
         <v>-0.280260975715766</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.367293985301159</v>
+        <v>-0.366804865395598</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.193227966130373</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
+        <v>-0.188516372799127</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.280260975715766</v>
       </c>
       <c r="F12" t="n">
-        <v>0.280260975715766</v>
+        <v>0.755586525988178</v>
       </c>
     </row>
     <row r="13">
@@ -1754,16 +1796,16 @@
         <v>0.129992573271486</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0802338235252673</v>
+        <v>0.0804270845089133</v>
       </c>
       <c r="D13" t="n">
-        <v>0.179751323017705</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
+        <v>0.173259329533849</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.129992573271486</v>
       </c>
       <c r="F13" t="n">
-        <v>0.129992573271486</v>
+        <v>1.1388199255868</v>
       </c>
     </row>
   </sheetData>
@@ -1817,28 +1859,28 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.433328144647614</v>
+        <v>0.445425942298677</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.34391575952003</v>
+        <v>-0.344153090175444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000000000000000000182097552403569</v>
+        <v>0.0000000000000000000134016028809071</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000000000162290492375171</v>
+        <v>0.0000000000156850731019498</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.777243904167644</v>
+        <v>-0.789579032474121</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000000000000000000946907272498557</v>
+        <v>0.0000000000000000000795091568655474</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000000000372313482507744</v>
+        <v>0.0000000000359834029985906</v>
       </c>
     </row>
     <row r="3">
@@ -1849,60 +1891,60 @@
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.260666307407242</v>
+        <v>-0.258015528607829</v>
       </c>
       <c r="D3" t="n">
-        <v>0.433608474439268</v>
+        <v>0.432746052076357</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000000153217703750053</v>
+        <v>0.000000206506726810557</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000000000450873096649201</v>
+        <v>0.00000000000000000533327668077606</v>
       </c>
       <c r="G3" t="n">
-        <v>0.69427478184651</v>
+        <v>0.690761580684186</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000000351499438014827</v>
+        <v>0.000000460214991177813</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0000000000000000125600362637992</v>
+        <v>0.0000000000000000148569850393047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>0.17653179733687</v>
+        <v>-0.412050008620979</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.397949832763833</v>
+        <v>0.179612021554358</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004305537589735</v>
+        <v>0.0000000000000000140013063477062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000000000000317574454885322</v>
+        <v>0.0005854480802592</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.574481630100703</v>
+        <v>0.591662030175336</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00062191098518395</v>
+        <v>0.000000000000000060672327506727</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00000000000000799058305840486</v>
+        <v>0.0007739822078003</v>
       </c>
     </row>
     <row r="5">
@@ -1913,156 +1955,156 @@
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0884881288829218</v>
+        <v>0.102802200550213</v>
       </c>
       <c r="D5" t="n">
-        <v>0.659088606938053</v>
+        <v>0.658719046945885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0793788910719774</v>
+        <v>0.0414013077005388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000000000000000000000000000135098543715383</v>
+        <v>0.000000000000000000000000000000000000000000000157891818054203</v>
       </c>
       <c r="G5" t="n">
-        <v>0.570600478055131</v>
+        <v>0.555916846395672</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0938114167214278</v>
+        <v>0.0538217000107004</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00000000000000000000000000000000000000000000131721080122499</v>
+        <v>0.00000000000000000000000000000000000000000000153944522602848</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" t="n">
-        <v>-0.543854347875337</v>
+        <v>-0.539949178901385</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00069763580379724</v>
+        <v>-0.0000870039501538385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00000000000000000000000000000010425210530499</v>
+        <v>0.00000000000000000000000000000033979694494757</v>
       </c>
       <c r="F6" t="n">
-        <v>0.989431605429316</v>
+        <v>0.998681950626344</v>
       </c>
       <c r="G6" t="n">
-        <v>0.54315671207154</v>
+        <v>0.539862174951231</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000000000000000000000000000000903518245976579</v>
+        <v>0.00000000000000000000000000000240946924599186</v>
       </c>
       <c r="J6" t="n">
-        <v>0.989431605429316</v>
+        <v>0.998681950626344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" t="n">
-        <v>-0.101124598852631</v>
+        <v>-0.11794078371344</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.641990941393774</v>
+        <v>-0.641707870951536</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0448526826347084</v>
+        <v>0.0191910842107014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000000000000000000000000000000000000000000146540665924938</v>
+        <v>0.000000000000000000000000000000000000000000163903782140468</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.540866342541143</v>
+        <v>-0.523767087238096</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0546642069610508</v>
+        <v>0.0262614836567492</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00000000000000000000000000000000000000000103910654019502</v>
+        <v>0.00000000000000000000000000000000000000000116222681881423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.219220701592887</v>
+        <v>0.127166105714794</v>
       </c>
       <c r="D8" t="n">
-        <v>0.308221508027758</v>
+        <v>0.621884680677865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000112774282987496</v>
+        <v>0.0115231682012149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00000000198752689695744</v>
+        <v>0.000000000000000000000000000000000000000314112377768806</v>
       </c>
       <c r="G8" t="n">
-        <v>0.527442209620645</v>
+        <v>0.494718574963071</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0000219909851825618</v>
+        <v>0.0163419476308138</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00000000387567744906701</v>
+        <v>0.00000000000000000000000000000000000000188467426661284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>0.101718051609301</v>
+        <v>0.0491513037488628</v>
       </c>
       <c r="D9" t="n">
-        <v>0.62210734517822</v>
+        <v>-0.397587443494676</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0436050990833498</v>
+        <v>0.330496647133703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000000000000000000000000000000000000000289412321096512</v>
+        <v>0.00000000000000338123644908975</v>
       </c>
       <c r="G9" t="n">
-        <v>0.520389293568918</v>
+        <v>-0.446738747243539</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0539872655317664</v>
+        <v>0.358038034394845</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00000000000000000000000000000000000000173647392657907</v>
+        <v>0.00000000000000850762719448388</v>
       </c>
     </row>
     <row r="10">
@@ -2073,380 +2115,380 @@
         <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.069979004844365</v>
+        <v>-0.0469751726884139</v>
       </c>
       <c r="D10" t="n">
-        <v>0.38885404528546</v>
+        <v>0.388566532253387</v>
       </c>
       <c r="E10" t="n">
-        <v>0.165646068472733</v>
+        <v>0.35238067006518</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0000000000000149728060152447</v>
+        <v>0.000000000000015712809393912</v>
       </c>
       <c r="G10" t="n">
-        <v>0.458833050129825</v>
+        <v>0.435541704941801</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.184577047726759</v>
+        <v>0.376516332398411</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0000000000000364962146621589</v>
+        <v>0.0000000000000382999728976604</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.203595404805567</v>
+        <v>0.0122707783582706</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.649350411189755</v>
+        <v>0.432016019686947</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000467851495228971</v>
+        <v>0.808157805190573</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00000000000000000000000000000000000000000000764542999705496</v>
+        <v>0.000000000000000006145742720502</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.445755006384188</v>
+        <v>0.419745241328676</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000729848332557195</v>
+        <v>0.818653361102138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0000000000000000000000000000000000000000000662603933078097</v>
+        <v>0.0000000000000000165299286965226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.207625362883119</v>
+        <v>-0.0352137777613839</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.647174629893175</v>
+        <v>-0.451518233962364</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000327428180382163</v>
+        <v>0.485822246458662</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0000000000000000000000000000000000000000000184616443576512</v>
+        <v>0.000000000000000000123422292525152</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.439549267010055</v>
+        <v>-0.41630445620098</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0000543391448293802</v>
+        <v>0.505255136317009</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000000000000000000000000000000000000000000144000825989679</v>
+        <v>0.000000000000000000356553289517105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.443207536028905</v>
+        <v>-0.236552719881628</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0110745929184504</v>
+        <v>-0.64907813020479</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0000000000000000000217948235103248</v>
+        <v>0.00000205363623690965</v>
       </c>
       <c r="F13" t="n">
-        <v>0.83345066824799</v>
+        <v>0.00000000000000000000000000000000000000000000854056099118895</v>
       </c>
       <c r="G13" t="n">
-        <v>0.432132943110454</v>
+        <v>-0.412525410323162</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000000000000000000130768941061949</v>
+        <v>0.0000038138958685465</v>
       </c>
       <c r="J13" t="n">
-        <v>0.866788694977909</v>
+        <v>0.0000000000000000000000000000000000000000000740181952569709</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00383674269678863</v>
+        <v>-0.235819748997672</v>
       </c>
       <c r="D14" t="n">
-        <v>0.432297270554491</v>
+        <v>-0.647275497453637</v>
       </c>
       <c r="E14" t="n">
-        <v>0.939486342297598</v>
+        <v>0.0000022130041165409</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00000000000000000581925934908202</v>
+        <v>0.0000000000000000000000000000000000000000000177251528395722</v>
       </c>
       <c r="G14" t="n">
-        <v>0.428460527857702</v>
+        <v>-0.411455748455964</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.939486342297598</v>
+        <v>0.00000401428653698116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0000000000000000156518010078758</v>
+        <v>0.000000000000000000000000000000000000000000138256192148663</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.209931755766601</v>
+        <v>-0.420164870185783</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.630870431742532</v>
+        <v>-0.0104425474394261</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000266104375706555</v>
+        <v>0.00000000000000000277132017359403</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0000000000000000000000000000000000000000109306561073732</v>
+        <v>0.84282877300874</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.420938675975931</v>
+        <v>0.409722322746357</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0000482700960583984</v>
+        <v>0.0000000000000000127154690317844</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0000000000000000000000000000000000000000710492646979258</v>
+        <v>0.87654192392909</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
       <c r="C16" t="n">
-        <v>-0.421160456552527</v>
+        <v>-0.401393484506365</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00193893524521357</v>
+        <v>-0.00178794121116427</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00000000000000000226494785886618</v>
+        <v>0.000000000000000109998932003459</v>
       </c>
       <c r="F16" t="n">
-        <v>0.970633071367976</v>
+        <v>0.972919100973791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.419221521307314</v>
+        <v>0.399605543295201</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0000000000000000110416208119726</v>
+        <v>0.000000000000000451574562961569</v>
       </c>
       <c r="J16" t="n">
-        <v>0.983238695671456</v>
+        <v>0.985554413973451</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0432235244865768</v>
+        <v>-0.445140161042946</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.45181230397357</v>
+        <v>-0.0557230319625884</v>
       </c>
       <c r="E17" t="n">
-        <v>0.392198894804346</v>
+        <v>0.0000000000000000000142708743092008</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000000000000000000116133513621263</v>
+        <v>0.289678333541808</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.408588779486993</v>
+        <v>0.389417129080358</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.41339883506404</v>
+        <v>0.0000000000000000000795091568655474</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000000000000000000335496817128092</v>
+        <v>0.309519315291247</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0741580421680395</v>
+        <v>-0.244443515724674</v>
       </c>
       <c r="D18" t="n">
-        <v>0.474545769928451</v>
+        <v>-0.63118491144044</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14174003687664</v>
+        <v>0.000000904501934840247</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000000000000000000000874878075850505</v>
+        <v>0.00000000000000000000000000000000000000000969916371828866</v>
       </c>
       <c r="G18" t="n">
-        <v>0.400387727760412</v>
+        <v>-0.386741395715766</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.160227867773594</v>
+        <v>0.0000018090038696805</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00000000000000000000262463422755152</v>
+        <v>0.0000000000000000000000000000000000000000630445641688763</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.452636249493838</v>
+        <v>-0.0772738508146577</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0559103791297758</v>
+        <v>0.308412148869326</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00000000000000000000269118326329238</v>
+        <v>0.125705360813901</v>
       </c>
       <c r="F19" t="n">
-        <v>0.288057310829223</v>
+        <v>0.0000000019403278753922</v>
       </c>
       <c r="G19" t="n">
-        <v>0.396725870364063</v>
+        <v>0.385685999683984</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0000000000000000000174926912114005</v>
+        <v>0.148560880961884</v>
       </c>
       <c r="J19" t="n">
-        <v>0.307787263625745</v>
+        <v>0.00000000378363935701479</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.266613483845306</v>
+        <v>0.0944744301567859</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.615539432704243</v>
+        <v>0.472138853257594</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000000774926978067216</v>
+        <v>0.0609996468973959</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00000000000000000000000000000000000000315326546783494</v>
+        <v>0.00000000000000000000149382441743085</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.348925948858937</v>
+        <v>0.377664423100808</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000000183164558452251</v>
+        <v>0.0767414912580142</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0000000000000000000000000000000000000175681933207947</v>
+        <v>0.00000000000000000000448147325229254</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.398013338203292</v>
+        <v>-0.277417839202953</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0644331693312858</v>
+        <v>-0.615391356871775</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00000000000000020830272484754</v>
+        <v>0.0000000215131346574166</v>
       </c>
       <c r="F21" t="n">
-        <v>0.220705000568607</v>
+        <v>0.00000000000000000000000000000000000000332555788075836</v>
       </c>
       <c r="G21" t="n">
-        <v>0.333580168872006</v>
+        <v>-0.337973517668821</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000000000000000855137502005692</v>
+        <v>0.000000054129822686403</v>
       </c>
       <c r="J21" t="n">
-        <v>0.24246464851199</v>
+        <v>0.0000000000000000000000000000000000000185281081927966</v>
       </c>
     </row>
     <row r="22">
@@ -2454,351 +2496,351 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.11862800890427</v>
+        <v>0.231736226126446</v>
       </c>
       <c r="D22" t="n">
-        <v>0.212868492835321</v>
+        <v>-0.0919181675350443</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0184957800950696</v>
+        <v>0.00000334117483760124</v>
       </c>
       <c r="F22" t="n">
-        <v>0.000043387775287414</v>
+        <v>0.0803013340299399</v>
       </c>
       <c r="G22" t="n">
-        <v>0.331496501739591</v>
+        <v>-0.32365439366149</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0244520482612784</v>
+        <v>0.00000592299175756584</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0000604329727217552</v>
+        <v>0.091479035482868</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.129576632621945</v>
+        <v>-0.584273760505069</v>
       </c>
       <c r="D23" t="n">
-        <v>0.179209222597303</v>
+        <v>-0.263917264835748</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0100323017156803</v>
+        <v>0.000000000000000000000000000000000000194663655530642</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00060262575059386</v>
+        <v>0.000000336635643722336</v>
       </c>
       <c r="G23" t="n">
-        <v>0.308785855219248</v>
+        <v>0.320356495669321</v>
       </c>
       <c r="H23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0134917161003976</v>
+        <v>0.00000000000000000000000000000000000168708501459889</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00079669167027663</v>
+        <v>0.000000596763186598687</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.408003435093671</v>
+        <v>-0.369994588922748</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.715988881021492</v>
+        <v>-0.0650493228475328</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000000000000000030895121585042</v>
+        <v>0.0000000000000315141590584071</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000265301960639342</v>
+        <v>0.21631312579717</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.307985445927822</v>
+        <v>0.304945266075215</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.000000000000000133878860201849</v>
+        <v>0.000000000000117052590788369</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000029562218471241</v>
+        <v>0.237639772002525</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
       <c r="C25" t="n">
-        <v>0.211122008970254</v>
+        <v>-0.081205625031116</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0916778691868418</v>
+        <v>0.212351290218296</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0000238882297422384</v>
+        <v>0.107523821885697</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0810982940323001</v>
+        <v>0.0000453291888222099</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.302799878157096</v>
+        <v>0.293556915249412</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0000443638552355856</v>
+        <v>0.129028586262836</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0941294115605531</v>
+        <v>0.0000631370844309352</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0840333429749799</v>
+        <v>-0.227061497005428</v>
       </c>
       <c r="D26" t="n">
-        <v>0.216096810082858</v>
+        <v>-0.511221613926332</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0957807881881216</v>
+        <v>0.00000530580026956437</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0000329352111265224</v>
+        <v>0.000000000000000000000000146017554573618</v>
       </c>
       <c r="G26" t="n">
-        <v>0.300130153057838</v>
+        <v>-0.284160116920904</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.109866198215786</v>
+        <v>0.00000899679176143523</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0000467081175976136</v>
+        <v>0.000000000000000000000000542350916987723</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.283194922108371</v>
+        <v>-0.0897957986804975</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00610325498587233</v>
+        <v>-0.36986983973466</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000000010594118469666</v>
+        <v>0.0750218558639923</v>
       </c>
       <c r="F27" t="n">
-        <v>0.907745549466225</v>
+        <v>0.000000000000327617089530819</v>
       </c>
       <c r="G27" t="n">
-        <v>0.289298177094243</v>
+        <v>-0.280074041054162</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0000000275447080211316</v>
+        <v>0.0928842024982762</v>
       </c>
       <c r="J27" t="n">
-        <v>0.931633590241652</v>
+        <v>0.000000000000774367666163753</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C28" t="n">
-        <v>0.234837658134729</v>
+        <v>-0.441745057878795</v>
       </c>
       <c r="D28" t="n">
-        <v>0.517849793055391</v>
+        <v>-0.715866642353574</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00000244516661370678</v>
+        <v>0.0000000000000000000299736744664514</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0000000000000000000000000270202218910054</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000283114058609671</v>
       </c>
       <c r="G28" t="n">
-        <v>0.283012134920662</v>
+        <v>-0.274121584474779</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00000501902620708235</v>
+        <v>0.000000000000000000146121663023951</v>
       </c>
       <c r="J28" t="n">
-        <v>0.000000000000000000000000105378865374921</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000315469951022204</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.105547200917723</v>
+        <v>-0.0565777352959691</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.371988686990842</v>
+        <v>0.214576710034329</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0362378442955318</v>
+        <v>0.262558062514998</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00000000000023447604627285</v>
+        <v>0.0000375189725374732</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.266441486073119</v>
+        <v>0.271154445330298</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0455895460492174</v>
+        <v>0.292564698230998</v>
       </c>
       <c r="J29" t="n">
-        <v>0.000000000000554216109372192</v>
+        <v>0.0000532087246895074</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0869770731340445</v>
+        <v>0.0366088069256805</v>
       </c>
       <c r="D30" t="n">
-        <v>0.178700487341827</v>
+        <v>-0.226418949906841</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0846664813601104</v>
+        <v>0.468698555155613</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00062498873096257</v>
+        <v>0.0000132656009885989</v>
       </c>
       <c r="G30" t="n">
-        <v>0.265677560475871</v>
+        <v>-0.263027756832522</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0985669484490838</v>
+        <v>0.494033612191051</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00081248535025134</v>
+        <v>0.0000206943375422143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.385044873204772</v>
+        <v>-0.255158627064199</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.119752709416302</v>
+        <v>0.0057259213174199</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00000000000000225743824617362</v>
+        <v>0.000000283819252403805</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0224926531358265</v>
+        <v>0.913426099928551</v>
       </c>
       <c r="G31" t="n">
-        <v>0.26529216378847</v>
+        <v>0.260884548381619</v>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00000000000000838477062864487</v>
+        <v>0.000000598321667229642</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0265822264332495</v>
+        <v>0.93746362887404</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
       </c>
       <c r="C32" t="n">
-        <v>0.336945871756182</v>
+        <v>0.25698639546051</v>
       </c>
       <c r="D32" t="n">
-        <v>0.589325983015902</v>
+        <v>0.517216400299929</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00000000000647368254840164</v>
+        <v>0.000000231672679835664</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0000000000000000000000000000000000254391597743751</v>
+        <v>0.0000000000000000000000000317982647958972</v>
       </c>
       <c r="G32" t="n">
-        <v>0.25238011125972</v>
+        <v>0.26023000483942</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0000000000219542277728403</v>
+        <v>0.000000501957472977272</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000000000000000000000000000000000124015903900079</v>
+        <v>0.000000000000000000000000124013232703999</v>
       </c>
     </row>
     <row r="33">
@@ -2809,28 +2851,28 @@
         <v>25</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.50731104080159</v>
+        <v>-0.509483213639671</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.257180258106897</v>
+        <v>-0.25710896674026</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00000000000000000000000000370390858272433</v>
+        <v>0.00000000000000000000000000205733209175056</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000000680550796028591</v>
+        <v>0.000000685567272927885</v>
       </c>
       <c r="G33" t="n">
-        <v>0.250130782694693</v>
+        <v>0.25237424689941</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0000000000000000000000000288904869452498</v>
+        <v>0.0000000000000000000000000133726585963787</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00000117962137978289</v>
+        <v>0.00000118831660640833</v>
       </c>
     </row>
     <row r="34">
@@ -2838,383 +2880,383 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0691874374647225</v>
+        <v>-0.0716807593299764</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.17587771117806</v>
+        <v>0.178434459150977</v>
       </c>
       <c r="E34" t="n">
-        <v>0.170496276946355</v>
+        <v>0.155570087042077</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00076367613752151</v>
+        <v>0.0006369866228405</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.245065148642782</v>
+        <v>0.250115218480953</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.187305769039657</v>
+        <v>0.175861837525826</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00097650391355209</v>
+        <v>0.00082808260969265</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C35" t="n">
-        <v>0.642192509144264</v>
+        <v>0.0756736130579796</v>
       </c>
       <c r="D35" t="n">
-        <v>0.883643238264277</v>
+        <v>-0.174012881446474</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0000000000000000000000000000000000000000000000342139549446413</v>
+        <v>0.133755221559222</v>
       </c>
       <c r="F35" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000488560746109939</v>
+        <v>0.00087035827295471</v>
       </c>
       <c r="G35" t="n">
-        <v>0.241450729120013</v>
+        <v>-0.249686494504454</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.000000000000000000000000000000000000000000000333586060710252</v>
+        <v>0.15571503405402</v>
       </c>
       <c r="J35" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000635128969942921</v>
+        <v>0.00111291713590931</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>0.100269994825867</v>
+        <v>-0.36632543701146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.338810369324105</v>
+        <v>-0.120261107963465</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0467018545993918</v>
+        <v>0.0000000000000587102165090043</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0000000000335572681070706</v>
+        <v>0.0219228196594897</v>
       </c>
       <c r="G36" t="n">
-        <v>0.238540374498238</v>
+        <v>0.246064329047995</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0560422255192702</v>
+        <v>0.000000000000199104212508797</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000000000070742348982473</v>
+        <v>0.0259087868703061</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.279470471330248</v>
+        <v>0.641811105409988</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.511880865670939</v>
+        <v>0.883464299072213</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0000000167573825969193</v>
+        <v>0.0000000000000000000000000000000000000000000000403063071422929</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00000000000000000000000012366420739894</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000633896621033838</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.232410394340691</v>
+        <v>0.241653193662225</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0000000421637368567648</v>
+        <v>0.000000000000000000000000000000000000000000000392986494637356</v>
       </c>
       <c r="J37" t="n">
-        <v>0.000000000000000000000000459324198910347</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000082406560734399</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C38" t="n">
-        <v>0.724857646595383</v>
+        <v>0.738136204662758</v>
       </c>
       <c r="D38" t="n">
-        <v>0.948243356022569</v>
+        <v>0.501671666145255</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000199836904873999</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000543479608437579</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000627065060555204</v>
+        <v>0.00000000000000000000000155713335179653</v>
       </c>
       <c r="G38" t="n">
-        <v>0.223385709427186</v>
+        <v>-0.236464538517503</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000389681964504297</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000105978523645328</v>
       </c>
       <c r="J38" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000489110747233059</v>
+        <v>0.00000000000000000000000528071310609258</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C39" t="n">
-        <v>0.717045865707725</v>
+        <v>-0.266842208228013</v>
       </c>
       <c r="D39" t="n">
-        <v>0.501760913808038</v>
+        <v>-0.49306030090175</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000020046286194675</v>
+        <v>0.0000000754622606165325</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0000000000000000000000015235912464789</v>
+        <v>0.0000000000000000000000123569413333414</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.215284951899687</v>
+        <v>-0.226218092673736</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000031272206463693</v>
+        <v>0.00000017836534327544</v>
       </c>
       <c r="J39" t="n">
-        <v>0.00000000000000000000000516696161849368</v>
+        <v>0.0000000000000000000000385536569600252</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.297757515575607</v>
+        <v>0.727620639313635</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.505696686949516</v>
+        <v>0.949506752781225</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00000000165154309537359</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000376848191333345</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000000000000000000000000579467087188448</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000813362639019329</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.207939171373909</v>
+        <v>0.22188611346759</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.00000000444208142893587</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000587883178480018</v>
       </c>
       <c r="J40" t="n">
-        <v>0.00000000000000000000000205447421821359</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000634422858435077</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C41" t="n">
-        <v>0.330838635791337</v>
+        <v>0.367818535974343</v>
       </c>
       <c r="D41" t="n">
-        <v>0.533942287842995</v>
+        <v>0.589183243929658</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0000000000161987561727382</v>
+        <v>0.0000000000000456218191912944</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000000000000000000000000000384003253091705</v>
+        <v>0.0000000000000000000000000000000000266567538501289</v>
       </c>
       <c r="G41" t="n">
-        <v>0.203103652051658</v>
+        <v>0.221364707955315</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0000000000526459575613991</v>
+        <v>0.00000000000016175008622368</v>
       </c>
       <c r="J41" t="n">
-        <v>0.00000000000000000000000000166401409673072</v>
+        <v>0.000000000000000000000000000000000129951675019379</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.204317684290033</v>
+        <v>-0.283930106182109</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.406134837942496</v>
+        <v>-0.504774533577651</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0000439087320346134</v>
+        <v>0.00000000966957480114807</v>
       </c>
       <c r="F42" t="n">
-        <v>0.000000000000000754883333896414</v>
+        <v>0.000000000000000000000000727589141072677</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.201817153652463</v>
+        <v>-0.220844427395541</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0000698955326265274</v>
+        <v>0.000000025140894482985</v>
       </c>
       <c r="J42" t="n">
-        <v>0.00000000000000196269666813068</v>
+        <v>0.00000000000000000000000257963422743949</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0263184572296561</v>
+        <v>0.319624924190982</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.226021783556177</v>
+        <v>0.533544253975883</v>
       </c>
       <c r="E43" t="n">
-        <v>0.602480407790044</v>
+        <v>0.0000000000828254271989963</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0000137489264678822</v>
+        <v>0.000000000000000000000000000427788540437285</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.199703326326521</v>
+        <v>0.213919329784901</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.626579624101645</v>
+        <v>0.000000000230727975768633</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0000218860462141798</v>
+        <v>0.0000000000000000000000000018537503418949</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C44" t="n">
-        <v>0.693754553864439</v>
+        <v>0.132730461644487</v>
       </c>
       <c r="D44" t="n">
-        <v>0.889460842550734</v>
+        <v>0.33856235248575</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000077086235630056</v>
+        <v>0.00834126292332611</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000807418849182188</v>
+        <v>0.0000000000347509501425472</v>
       </c>
       <c r="G44" t="n">
-        <v>0.195706288686295</v>
+        <v>0.205831890841263</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000100212106319073</v>
+        <v>0.0122758209060271</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000125957340472421</v>
+        <v>0.0000000000732587597599644</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.023049477647874</v>
+        <v>0.690184686282777</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.216881393621094</v>
+        <v>0.889334456096226</v>
       </c>
       <c r="E45" t="n">
-        <v>0.648299353920399</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000496720124066651</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0000307818718068824</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000980604117972546</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.19383191597322</v>
+        <v>0.199149769813448</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.656718826049235</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000645736161286647</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0000444627037210523</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000152974242403717</v>
       </c>
     </row>
     <row r="46">
@@ -3222,191 +3264,191 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C46" t="n">
-        <v>0.197105264528907</v>
+        <v>-0.0235163908202505</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0188493859255354</v>
+        <v>-0.217979135506081</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0000819231953742219</v>
+        <v>0.641667729023395</v>
       </c>
       <c r="F46" t="n">
-        <v>0.720401533979785</v>
+        <v>0.0000279916901263315</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.178255878603372</v>
+        <v>-0.19446274468583</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.00012529429880763</v>
+        <v>0.658553721892432</v>
       </c>
       <c r="J46" t="n">
-        <v>0.759342157438152</v>
+        <v>0.0000411953175444124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.316353354355417</v>
+        <v>-0.231466571428472</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.493553963867032</v>
+        <v>-0.405962683715804</v>
       </c>
       <c r="E47" t="n">
-        <v>0.000000000131662312086262</v>
+        <v>0.00000343241574949858</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0000000000000000000000109907167792571</v>
+        <v>0.000000000000000778361408449494</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.177200609511614</v>
+        <v>-0.174496112287332</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.000000000394986936258787</v>
+        <v>0.0000059495206324642</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0000000000000000000000342910363512822</v>
+        <v>0.00000000000000202373966196868</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.440989585133462</v>
+        <v>-0.0740664593009344</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.264492045786966</v>
+        <v>0.0941422722939419</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0000000000000000000353154555765444</v>
+        <v>0.142233985684106</v>
       </c>
       <c r="F48" t="n">
-        <v>0.000000316726006606274</v>
+        <v>0.0732218473917972</v>
       </c>
       <c r="G48" t="n">
-        <v>0.176497539346496</v>
+        <v>0.168208731594876</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.000000000000000000196757538212176</v>
+        <v>0.16315074828471</v>
       </c>
       <c r="J48" t="n">
-        <v>0.000000561468829892941</v>
+        <v>0.0852433447247788</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0237032252883969</v>
+        <v>0.182572976132509</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.151702396385839</v>
+        <v>0.0192483219208189</v>
       </c>
       <c r="E49" t="n">
-        <v>0.639022014107683</v>
+        <v>0.00026935118085594</v>
       </c>
       <c r="F49" t="n">
-        <v>0.00376586833277701</v>
+        <v>0.714739100376651</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.175405621674236</v>
+        <v>-0.16332465421169</v>
       </c>
       <c r="H49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.655838382899991</v>
+        <v>0.00042876310421967</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00466250365010487</v>
+        <v>0.753373646342957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
         <v>27</v>
       </c>
-      <c r="B50" t="s">
-        <v>18</v>
-      </c>
       <c r="C50" t="n">
-        <v>-0.0550748633534301</v>
+        <v>0.0115497817547735</v>
       </c>
       <c r="D50" t="n">
-        <v>0.091254831173604</v>
+        <v>-0.150152415756819</v>
       </c>
       <c r="E50" t="n">
-        <v>0.27546682451097</v>
+        <v>0.819229693756863</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0825168459455795</v>
+        <v>0.00414130404352512</v>
       </c>
       <c r="G50" t="n">
-        <v>0.146329694527034</v>
+        <v>-0.161702197511593</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.294334415230899</v>
+        <v>0.819229693756863</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0941294115605531</v>
+        <v>0.005127328815793</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
         <v>26</v>
       </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
       <c r="C51" t="n">
-        <v>0.355669356799941</v>
+        <v>0.34585681895223</v>
       </c>
       <c r="D51" t="n">
-        <v>0.49912305309762</v>
+        <v>0.498319976796794</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0000000000003420828702803</v>
+        <v>0.00000000000163683900550089</v>
       </c>
       <c r="F51" t="n">
-        <v>0.00000000000000000000000289218740239722</v>
+        <v>0.00000000000000000000000351149197563744</v>
       </c>
       <c r="G51" t="n">
-        <v>0.143453696297679</v>
+        <v>0.152463157844564</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00000000000121283926735743</v>
+        <v>0.00000000000531972676787788</v>
       </c>
       <c r="J51" t="n">
-        <v>0.00000000000000000000000939960905779096</v>
+        <v>0.0000000000000000000000114123489208217</v>
       </c>
     </row>
     <row r="52">
@@ -3414,63 +3456,63 @@
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C52" t="n">
-        <v>0.759133359964771</v>
+        <v>0.756486589817346</v>
       </c>
       <c r="D52" t="n">
-        <v>0.900033156840205</v>
+        <v>0.898381974378231</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000427245394547811</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000271814199211554</v>
       </c>
       <c r="F52" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000287570312717159</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000473805485988633</v>
       </c>
       <c r="G52" t="n">
-        <v>0.140899796875433</v>
+        <v>0.141895384560885</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000111083802582431</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000706716917950041</v>
       </c>
       <c r="J52" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000112152421959692</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000123189426357045</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
       </c>
       <c r="C53" t="n">
-        <v>0.759396430097307</v>
+        <v>0.757432378927848</v>
       </c>
       <c r="D53" t="n">
-        <v>0.898521991445523</v>
+        <v>0.898766840826964</v>
       </c>
       <c r="E53" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000355007593030366</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000140703739623644</v>
       </c>
       <c r="F53" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000037430702601062</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000247655989625346</v>
       </c>
       <c r="G53" t="n">
-        <v>0.139125561348216</v>
+        <v>0.141334461899116</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000111083802582431</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000548744584532212</v>
       </c>
       <c r="J53" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000729898700720708</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000965858359538848</v>
       </c>
     </row>
     <row r="54">
@@ -3481,796 +3523,796 @@
         <v>26</v>
       </c>
       <c r="C54" t="n">
-        <v>0.388603250359561</v>
+        <v>0.379249850448376</v>
       </c>
       <c r="D54" t="n">
-        <v>0.520879810813398</v>
+        <v>0.520540679472597</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00000000000000118625453134272</v>
+        <v>0.00000000000000633110721608893</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0000000000000000000000000123409216895652</v>
+        <v>0.0000000000000000000000000134775142000113</v>
       </c>
       <c r="G54" t="n">
-        <v>0.132276560453837</v>
+        <v>0.141290829024221</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0.00000000000000462639267223659</v>
+        <v>0.0000000000000246913181427468</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0000000000000000000000000506627311466361</v>
+        <v>0.0000000000000000000000000553287425053094</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0678895414258061</v>
+        <v>-0.152864126063924</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0625901275335091</v>
+        <v>-0.28418325861987</v>
       </c>
       <c r="E55" t="n">
-        <v>0.178677107187635</v>
+        <v>0.00234601395372418</v>
       </c>
       <c r="F55" t="n">
-        <v>0.234221032162901</v>
+        <v>0.0000000359338909507807</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.130479668959315</v>
+        <v>-0.131319132555946</v>
       </c>
       <c r="H55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.193566866119938</v>
+        <v>0.00358802134098993</v>
       </c>
       <c r="J55" t="n">
-        <v>0.25373945150981</v>
+        <v>0.0000000666371606045336</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" t="s">
         <v>26</v>
       </c>
-      <c r="B56" t="s">
-        <v>25</v>
-      </c>
       <c r="C56" t="n">
-        <v>-0.250631644933667</v>
+        <v>-0.123307935845685</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.134129633636281</v>
+        <v>-0.251947060171474</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00000046613470266669</v>
+        <v>0.0143186048233436</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0105194766929049</v>
+        <v>0.00000116006313913118</v>
       </c>
       <c r="G56" t="n">
-        <v>0.116502011297386</v>
+        <v>-0.128639124325789</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.00000103881448022862</v>
+        <v>0.0199437710039429</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0126233720314859</v>
+        <v>0.00000196706358374417</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.194151355606633</v>
+        <v>-0.443990008313466</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.07784748964664</v>
+        <v>-0.32714804593459</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00010509478058026</v>
+        <v>0.000000000000000000018366950308513</v>
       </c>
       <c r="F57" t="n">
-        <v>0.13878636770843</v>
+        <v>0.000000000167916495256127</v>
       </c>
       <c r="G57" t="n">
-        <v>0.116303865959993</v>
+        <v>0.116841962378876</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0001576421708704</v>
+        <v>0.0000000000000000000955081416042677</v>
       </c>
       <c r="J57" t="n">
-        <v>0.154647666875107</v>
+        <v>0.000000000335832990512253</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.231128299783175</v>
+        <v>0.0503405688609349</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.341050400580039</v>
+        <v>-0.0592433348602047</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00000355024253304657</v>
+        <v>0.318915481828605</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0000000000244382626493713</v>
+        <v>0.260236123409657</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.109922100796864</v>
+        <v>-0.10958390372114</v>
       </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0.00000710048506609314</v>
+        <v>0.350357853276496</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0000000000529495690736377</v>
+        <v>0.281922467027128</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.413575283864318</v>
+        <v>-0.236741559277705</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.328326646065544</v>
+        <v>-0.13447127786927</v>
       </c>
       <c r="E59" t="n">
-        <v>0.000000000000000010360832927116</v>
+        <v>0.00000201439200426992</v>
       </c>
       <c r="F59" t="n">
-        <v>0.00000000014313850087434</v>
+        <v>0.0103221995247624</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0852486377987737</v>
+        <v>0.102270281408435</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0000000000000000475379393126498</v>
+        <v>0.0000038138958685465</v>
       </c>
       <c r="J59" t="n">
-        <v>0.000000000286277001748679</v>
+        <v>0.0123866394297149</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C60" t="n">
-        <v>0.47023478309839</v>
+        <v>-0.104603623396612</v>
       </c>
       <c r="D60" t="n">
-        <v>0.552083848895286</v>
+        <v>-0.204258671621209</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0000000000000000000000453995442752371</v>
+        <v>0.0379474043832503</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00000000000000000000000000000239547426837665</v>
+        <v>0.000088685059280882</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0818490657968955</v>
+        <v>-0.0996550482245969</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.000000000000000000000321924041224408</v>
+        <v>0.0501677549473478</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0000000000000000000000000000109909995843164</v>
+        <v>0.00012135850217383</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.135878478057905</v>
+        <v>-0.32536923451631</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.217027128210112</v>
+        <v>-0.238306027407309</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00691148381588414</v>
+        <v>0.0000000000362057790803554</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0000303968575592901</v>
+        <v>0.00000441149875172423</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0811486501522068</v>
+        <v>0.0870632071090014</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0094578199585783</v>
+        <v>0.000000000104594472898804</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0000444627037210523</v>
+        <v>0.00000732121069435086</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.208176917757099</v>
+        <v>-0.132296636890081</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.283308953651882</v>
+        <v>-0.216636674375746</v>
       </c>
       <c r="E62" t="n">
-        <v>0.000031165083599374</v>
+        <v>0.00855769384495398</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0000000397248626563635</v>
+        <v>0.0000314387927392203</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.0751320358947826</v>
+        <v>-0.084340037485665</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0000539559356998875</v>
+        <v>0.0123611133316002</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0000000720590531906128</v>
+        <v>0.0000454115895122071</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C63" t="n">
-        <v>0.669851901201676</v>
+        <v>-0.262028092023339</v>
       </c>
       <c r="D63" t="n">
-        <v>0.600568564101476</v>
+        <v>-0.340431815943987</v>
       </c>
       <c r="E63" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000122885736355558</v>
+        <v>0.000000131268226610246</v>
       </c>
       <c r="F63" t="n">
-        <v>0.000000000000000000000000000000000000594374606472919</v>
+        <v>0.0000000000266815582056911</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.0692833371002</v>
+        <v>-0.0784037239206476</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000136929820510479</v>
+        <v>0.000000301144755164683</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00000000000000000000000000000000000309074795365918</v>
+        <v>0.0000000000578100427789974</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.187664577727357</v>
+        <v>-0.145024015670317</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.252630979134997</v>
+        <v>-0.0783456874565094</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00017929109123873</v>
+        <v>0.00391707408290201</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00000108267872903374</v>
+        <v>0.136269374769806</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.0649664014076396</v>
+        <v>0.0666783282138071</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00026386236069096</v>
+        <v>0.00587561112435302</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00000183584654053547</v>
+        <v>0.151843017600641</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
         <v>26</v>
       </c>
-      <c r="B65" t="s">
-        <v>22</v>
-      </c>
       <c r="C65" t="n">
-        <v>-0.142875185713509</v>
+        <v>0.662634190325809</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.203948504262807</v>
+        <v>0.600353267317011</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00448916093236807</v>
+        <v>0.00000000000000000000000000000000000000000000000000368394358222581</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0000909492332493529</v>
+        <v>0.000000000000000000000000000000000000639602284541019</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.0610733185492985</v>
+        <v>-0.0622809230087977</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0.00636644641317653</v>
+        <v>0.0000000000000000000000000000000000000000000000000410496570590876</v>
       </c>
       <c r="J65" t="n">
-        <v>0.00012445684549911</v>
+        <v>0.0000000000000000000000000000000000033259318796133</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.206104781222</v>
+        <v>-0.275364261279887</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.239370788480793</v>
+        <v>-0.337478302603006</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0000374931542241149</v>
+        <v>0.0000000275653758879072</v>
       </c>
       <c r="F66" t="n">
-        <v>0.00000398586597677981</v>
+        <v>0.0000000000404723516172392</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0332660072587937</v>
+        <v>-0.0621140413231189</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0000609263756141867</v>
+        <v>0.0000000671906037267738</v>
       </c>
       <c r="J66" t="n">
-        <v>0.00000661484140827288</v>
+        <v>0.0000000000830748270038068</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.309820953438745</v>
+        <v>-0.164352258957285</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.342906190654097</v>
+        <v>-0.224757527729746</v>
       </c>
       <c r="E67" t="n">
-        <v>0.000000000326684778461019</v>
+        <v>0.00105951764614143</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0000000000187559041389702</v>
+        <v>0.0000154012593939503</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0330852372153521</v>
+        <v>-0.0604052687724614</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.000000000943756026665166</v>
+        <v>0.00165284752798063</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0000000000417988720811335</v>
+        <v>0.0000235548673083946</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
         <v>27</v>
       </c>
-      <c r="B68" t="s">
-        <v>14</v>
-      </c>
       <c r="C68" t="n">
-        <v>0.110076498677731</v>
+        <v>0.0885372373217003</v>
       </c>
       <c r="D68" t="n">
-        <v>0.141635706822633</v>
+        <v>0.14414992313174</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0289140245383263</v>
+        <v>0.079211640968085</v>
       </c>
       <c r="F68" t="n">
-        <v>0.00687469269813887</v>
+        <v>0.00593527214321326</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0315592081449023</v>
+        <v>0.0556126858100399</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0369720313768762</v>
+        <v>0.0965391874298536</v>
       </c>
       <c r="J68" t="n">
-        <v>0.00837853172585675</v>
+        <v>0.00723361292454116</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C69" t="n">
-        <v>0.116533847750556</v>
+        <v>-0.109042366689391</v>
       </c>
       <c r="D69" t="n">
-        <v>0.0910331007863793</v>
+        <v>-0.162033942636152</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0206858589008863</v>
+        <v>0.030463677413748</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0832683256112585</v>
+        <v>0.00195487097995048</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0255007469641764</v>
+        <v>-0.0529915759467603</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0268916165711521</v>
+        <v>0.0409683937633163</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0941294115605531</v>
+        <v>0.00245935381348608</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" t="s">
         <v>24</v>
       </c>
-      <c r="B70" t="s">
-        <v>25</v>
-      </c>
       <c r="C70" t="n">
-        <v>-0.138619012084672</v>
+        <v>0.319069283633091</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.161629758379804</v>
+        <v>0.283991103058612</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00584979446910995</v>
+        <v>0.000000000089644631082745</v>
       </c>
       <c r="F70" t="n">
-        <v>0.00200712770022212</v>
+        <v>0.0000000367358705896788</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.0230107462951326</v>
+        <v>-0.035078180574479</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.00814792801054601</v>
+        <v>0.000000000241113145670832</v>
       </c>
       <c r="J70" t="n">
-        <v>0.00252509613898912</v>
+        <v>0.0000000666371606045336</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.207944771186854</v>
+        <v>-0.331719219278336</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.18738336749792</v>
+        <v>-0.29701872261205</v>
       </c>
       <c r="E71" t="n">
-        <v>0.000031820167207626</v>
+        <v>0.0000000000142098813898526</v>
       </c>
       <c r="F71" t="n">
-        <v>0.00033110180469597</v>
+        <v>0.00000000791871833064294</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0205614036889339</v>
+        <v>0.034700496666286</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0000539559356998875</v>
+        <v>0.0000000000426296441695578</v>
       </c>
       <c r="J71" t="n">
-        <v>0.00044527484079803</v>
+        <v>0.0000000150648787753695</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C72" t="n">
-        <v>0.913252451018182</v>
+        <v>-0.244092606980222</v>
       </c>
       <c r="D72" t="n">
-        <v>0.899341553561009</v>
+        <v>-0.221136130644583</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000588830646152593</v>
+        <v>0.000000938657347388151</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000093540154846496</v>
+        <v>0.0000212413412926062</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0139108974571736</v>
+        <v>0.0229564763356383</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000459287903999022</v>
+        <v>0.0000018303818274069</v>
       </c>
       <c r="J72" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000024320440260089</v>
+        <v>0.0000318620119389093</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73" t="s">
         <v>17</v>
       </c>
-      <c r="B73" t="s">
-        <v>27</v>
-      </c>
       <c r="C73" t="n">
-        <v>-0.209067203833764</v>
+        <v>0.571867526904049</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.222493405359447</v>
+        <v>0.552618442430765</v>
       </c>
       <c r="E73" t="n">
-        <v>0.000028769274881784</v>
+        <v>0.0000000000000000000000000000000000135622249063629</v>
       </c>
       <c r="F73" t="n">
-        <v>0.000018841733471425</v>
+        <v>0.00000000000000000000000000000205285737097692</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.0134262015256828</v>
+        <v>-0.0192490844732831</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0000510000781995261</v>
+        <v>0.000000000000000000000000000000000105785354269631</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0000288167688386499</v>
+        <v>0.00000000000000000000000000000941899264330585</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.235953703717638</v>
+        <v>-0.203272735223298</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.22392762184398</v>
+        <v>-0.185769982799796</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0000021830216478279</v>
+        <v>0.0000481268698943206</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0000165865990098734</v>
+        <v>0.00037339493311535</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0120260818736584</v>
+        <v>0.0175027524235019</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.00000460204563596153</v>
+        <v>0.0000782061635782709</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0000258750944554025</v>
+        <v>0.0005021518066034</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
       </c>
       <c r="C75" t="n">
-        <v>0.272336977053334</v>
+        <v>-0.251730509283895</v>
       </c>
       <c r="D75" t="n">
-        <v>0.28414759774608</v>
+        <v>-0.236015557429278</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0000000395785756143264</v>
+        <v>0.000000413606872452868</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0000000360814358076815</v>
+        <v>0.0000054787523367734</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0118106206927465</v>
+        <v>0.0157149518546169</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0000000964727780599206</v>
+        <v>0.000000848982527666413</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0000000670083807856943</v>
+        <v>0.00000890297254725677</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.32529431803857</v>
+        <v>0.912353543118443</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.333174492980455</v>
+        <v>0.897747414593884</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0000000000366027735305075</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000405447718477608</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0000000000736909073630636</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000137305336859946</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.00788017494188498</v>
+        <v>-0.0146061285245587</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.000000000114200653415183</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000316249220412535</v>
       </c>
       <c r="J76" t="n">
-        <v>0.000000000151260283534709</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000267745406876894</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.245027758792676</v>
+        <v>-0.22358997998478</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.237379182708598</v>
+        <v>-0.228883539607213</v>
       </c>
       <c r="E77" t="n">
-        <v>0.000000850263990590535</v>
+        <v>0.00000743333438649487</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00000481699094722916</v>
+        <v>0.000010608634494603</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00764857608407751</v>
+        <v>-0.0052935596224335</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00000184223864627949</v>
+        <v>0.000012336171960566</v>
       </c>
       <c r="J77" t="n">
-        <v>0.00000782761028924738</v>
+        <v>0.0000168872140934497</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.216641975915442</v>
+        <v>0.0969126702382847</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.222028735840172</v>
+        <v>0.0917303299767083</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0000143664005762526</v>
+        <v>0.0545961809378002</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0000196327239021509</v>
+        <v>0.0809237621579217</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00538675992472964</v>
+        <v>-0.00518234026157638</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0000273312010962855</v>
+        <v>0.0698115100516134</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0000294490858532263</v>
+        <v>0.091479035482868</v>
       </c>
     </row>
     <row r="79">
@@ -4278,31 +4320,31 @@
         <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.299066929642397</v>
+        <v>-0.33805169489112</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.297970591639182</v>
+        <v>-0.342155840805788</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00000000139013299063085</v>
+        <v>0.00000000000547118693326102</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00000000705723354911983</v>
+        <v>0.0000000000208785472499007</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00109633800321496</v>
+        <v>-0.00410414591466823</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00000000387251333104309</v>
+        <v>0.0000000000170701032317744</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0000000134259565080816</v>
+        <v>0.0000000000465293338712072</v>
       </c>
     </row>
   </sheetData>
@@ -4362,25 +4404,25 @@
         <v>363</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1197</v>
+        <v>-2.3508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5761</v>
+        <v>-1.4809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6957</v>
+        <v>0.8699</v>
       </c>
       <c r="G2" t="n">
-        <v>4.96</v>
+        <v>7.41</v>
       </c>
       <c r="H2" t="s">
         <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000698727580091085</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K2" t="s">
         <v>57</v>
@@ -4397,25 +4439,25 @@
         <v>363</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.3404</v>
+        <v>-2.6519</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7751</v>
+        <v>-1.9742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5652</v>
+        <v>0.6777</v>
       </c>
       <c r="G3" t="n">
-        <v>3.67</v>
+        <v>4.76</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000434304567007542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K3" t="s">
         <v>57</v>
@@ -4432,25 +4474,25 @@
         <v>363</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9917</v>
+        <v>0.0545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1126</v>
+        <v>-0.5609</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1043</v>
+        <v>-0.6153</v>
       </c>
       <c r="G4" t="n">
-        <v>12.71</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000742776091162948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000350165871548247</v>
       </c>
       <c r="K4" t="s">
         <v>57</v>
@@ -4458,7 +4500,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" t="n">
         <v>394</v>
@@ -4467,25 +4509,25 @@
         <v>363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9894</v>
+        <v>3.2896</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5746</v>
+        <v>2.7319</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4148</v>
+        <v>-0.5577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000198232734348008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K5" t="s">
         <v>57</v>
@@ -4502,25 +4544,25 @@
         <v>363</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1939</v>
+        <v>-3.2896</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6139</v>
+        <v>-2.7319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.42</v>
+        <v>0.5577</v>
       </c>
       <c r="G6" t="n">
-        <v>2.63</v>
+        <v>3.61</v>
       </c>
       <c r="H6" t="s">
         <v>56</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000198232734348008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
@@ -4537,25 +4579,25 @@
         <v>363</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3907</v>
+        <v>-3.4146</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0806</v>
+        <v>-2.8671</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4713</v>
+        <v>0.5475</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>3.53</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000162221725106145</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000334582308031423</v>
       </c>
       <c r="K7" t="s">
         <v>57</v>
@@ -4572,25 +4614,25 @@
         <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2742</v>
+        <v>1.0696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3722</v>
+        <v>0.5529</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.902</v>
+        <v>-0.5166</v>
       </c>
       <c r="G8" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000513</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000305103479302289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000457655218953433</v>
       </c>
       <c r="K8" t="s">
         <v>57</v>
@@ -4607,25 +4649,25 @@
         <v>363</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9713</v>
+        <v>2.9812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1775</v>
+        <v>2.4728</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7938</v>
+        <v>-0.5084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000611</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000953196439177417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000185032249957969</v>
       </c>
       <c r="K9" t="s">
         <v>57</v>
@@ -4642,25 +4684,25 @@
         <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9713</v>
+        <v>3.0251</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1775</v>
+        <v>2.5284</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7938</v>
+        <v>-0.4967</v>
       </c>
       <c r="G10" t="n">
-        <v>6.22</v>
+        <v>0.32</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000611</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000550195339798033</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000864592676825481</v>
       </c>
       <c r="K10" t="s">
         <v>57</v>
@@ -4677,25 +4719,25 @@
         <v>363</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2119</v>
+        <v>-3.0251</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2414</v>
+        <v>-2.5284</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9705</v>
+        <v>0.4967</v>
       </c>
       <c r="G11" t="n">
-        <v>9.34</v>
+        <v>3.14</v>
       </c>
       <c r="H11" t="s">
         <v>56</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000478</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000550195339798033</v>
       </c>
       <c r="J11" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000864592676825481</v>
       </c>
       <c r="K11" t="s">
         <v>57</v>
@@ -4712,25 +4754,25 @@
         <v>363</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2742</v>
+        <v>2.6541</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3722</v>
+        <v>2.1757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.902</v>
+        <v>-0.4784</v>
       </c>
       <c r="G12" t="n">
-        <v>7.98</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000513</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000252069610214062</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000183</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000437805112477056</v>
       </c>
       <c r="K12" t="s">
         <v>57</v>
@@ -4747,25 +4789,25 @@
         <v>363</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9546</v>
+        <v>1.4829</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3722</v>
+        <v>1.0304</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5825</v>
+        <v>-0.4525</v>
       </c>
       <c r="G13" t="n">
-        <v>3.82</v>
+        <v>0.35</v>
       </c>
       <c r="H13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000727</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000238385115225527</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000002</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000342030817497495</v>
       </c>
       <c r="K13" t="s">
         <v>57</v>
@@ -4782,25 +4824,25 @@
         <v>363</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8636</v>
+        <v>-0.8638</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0403</v>
+        <v>-0.4587</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8233</v>
+        <v>0.4051</v>
       </c>
       <c r="G14" t="n">
-        <v>0.15</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000819</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407611296574457</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000204</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K14" t="s">
         <v>57</v>
@@ -4817,25 +4859,25 @@
         <v>363</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2728</v>
+        <v>0.305</v>
       </c>
       <c r="E15" t="n">
-        <v>0.521</v>
+        <v>0.6879</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7518</v>
+        <v>0.3828</v>
       </c>
       <c r="G15" t="n">
-        <v>0.18</v>
+        <v>2.41</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000865</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000845015956850821</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000204</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K15" t="s">
         <v>57</v>
@@ -4852,25 +4894,25 @@
         <v>363</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2864</v>
+        <v>0.2644</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6258</v>
+        <v>0.6418</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3394</v>
+        <v>0.3774</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="s">
         <v>56</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000157</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000262273675821503</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000345</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000865503130210961</v>
       </c>
       <c r="K16" t="s">
         <v>57</v>
@@ -4887,25 +4929,25 @@
         <v>363</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7386</v>
+        <v>-3.732</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0941</v>
+        <v>-3.3567</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8327</v>
+        <v>0.3753</v>
       </c>
       <c r="G17" t="n">
-        <v>0.15</v>
+        <v>2.37</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000199</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168706658373603</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000041</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K17" t="s">
         <v>57</v>
@@ -4922,25 +4964,25 @@
         <v>363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.313</v>
+        <v>0.0674</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0297</v>
+        <v>-0.3073</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2833</v>
+        <v>-0.3747</v>
       </c>
       <c r="G18" t="n">
-        <v>1.92</v>
+        <v>0.42</v>
       </c>
       <c r="H18" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000224</v>
+        <v>0.000000000000000000000000000000000000000681121390859979</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000434</v>
+        <v>0.000000000000000000000000000000000000000725064706399332</v>
       </c>
       <c r="K18" t="s">
         <v>57</v>
@@ -4957,25 +4999,25 @@
         <v>363</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1385</v>
+        <v>-1.1404</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5475</v>
+        <v>-0.8154</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.409</v>
+        <v>0.3251</v>
       </c>
       <c r="G19" t="n">
-        <v>0.39</v>
+        <v>2.11</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000283</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000223826440863733</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000468</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000410348474916844</v>
       </c>
       <c r="K19" t="s">
         <v>57</v>
@@ -4992,25 +5034,25 @@
         <v>363</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0268</v>
+        <v>1.3697</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7447</v>
+        <v>1.0485</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.282</v>
+        <v>-0.3212</v>
       </c>
       <c r="G20" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294455211529457</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000468</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000121462774755901</v>
       </c>
       <c r="K20" t="s">
         <v>57</v>
@@ -5027,25 +5069,25 @@
         <v>363</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0268</v>
+        <v>0.9442</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7447</v>
+        <v>1.2607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.282</v>
+        <v>0.3165</v>
       </c>
       <c r="G21" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="H21" t="s">
         <v>56</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000180149099655061</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000468</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000424637163472643</v>
       </c>
       <c r="K21" t="s">
         <v>57</v>
@@ -5062,25 +5104,25 @@
         <v>363</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4076</v>
+        <v>-0.7381</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7711</v>
+        <v>-0.4819</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1787</v>
+        <v>0.2562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07</v>
+        <v>1.8</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000459</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000840191745485496</v>
       </c>
       <c r="J22" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000721</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115526365004256</v>
       </c>
       <c r="K22" t="s">
         <v>57</v>
@@ -5097,25 +5139,25 @@
         <v>363</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1859</v>
+        <v>-0.3203</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5005</v>
+        <v>-0.0862</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6854</v>
+        <v>0.2341</v>
       </c>
       <c r="G23" t="n">
-        <v>0.21</v>
+        <v>1.71</v>
       </c>
       <c r="H23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000108</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000193966572888018</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000161</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000010668161508841</v>
       </c>
       <c r="K23" t="s">
         <v>57</v>
@@ -5132,25 +5174,25 @@
         <v>363</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1781</v>
+        <v>-0.3585</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.739</v>
+        <v>-0.1347</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4391</v>
+        <v>0.2237</v>
       </c>
       <c r="G24" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="s">
         <v>56</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000402</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000151448458936993</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000576</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000199911965796831</v>
       </c>
       <c r="K24" t="s">
         <v>57</v>
@@ -5167,25 +5209,25 @@
         <v>363</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0753</v>
+        <v>0.5371</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5518</v>
+        <v>0.3727</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5235</v>
+        <v>-0.1644</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="H25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000161</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411175586756774</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000221</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000904586290864904</v>
       </c>
       <c r="K25" t="s">
         <v>57</v>
@@ -5202,25 +5244,25 @@
         <v>363</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0127</v>
+        <v>2.6039</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3036</v>
+        <v>2.4503</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3163</v>
+        <v>-0.1536</v>
       </c>
       <c r="G26" t="n">
-        <v>2.07</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000121</v>
+        <v>0.0000000000130895411819585</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000016</v>
+        <v>0.0000000000130895411819585</v>
       </c>
       <c r="K26" t="s">
         <v>57</v>
@@ -5237,25 +5279,25 @@
         <v>363</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7003</v>
+        <v>-0.9657</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4001</v>
+        <v>-0.8456</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3002</v>
+        <v>0.1201</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5</v>
+        <v>1.32</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000415</v>
+        <v>0.00000000000000000000000000000000000242971859004497</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000527</v>
+        <v>0.00000000000000000000000000000000000250564729598388</v>
       </c>
       <c r="K27" t="s">
         <v>57</v>
@@ -5272,25 +5314,25 @@
         <v>363</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9408</v>
+        <v>1.0029</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7259</v>
+        <v>1.1186</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2149</v>
+        <v>0.1156</v>
       </c>
       <c r="G28" t="n">
-        <v>0.61</v>
+        <v>1.31</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000148</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000630344484191873</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000181</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K28" t="s">
         <v>57</v>
@@ -5307,25 +5349,25 @@
         <v>363</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.3117</v>
+        <v>1.9396</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9078</v>
+        <v>1.8312</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4038</v>
+        <v>-0.1084</v>
       </c>
       <c r="G29" t="n">
-        <v>2.53</v>
+        <v>0.78</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000363</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000317163919330143</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000037380033349624</v>
       </c>
       <c r="K29" t="s">
         <v>57</v>
@@ -5342,25 +5384,25 @@
         <v>363</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3525</v>
+        <v>-1.9396</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0525</v>
+        <v>-1.8312</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3</v>
+        <v>0.1084</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="H30" t="s">
         <v>56</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000022</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000317163919330143</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000251</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000037380033349624</v>
       </c>
       <c r="K30" t="s">
         <v>57</v>
@@ -5377,25 +5419,25 @@
         <v>363</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6692</v>
+        <v>0.9718</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5416</v>
+        <v>1.0668</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1276</v>
+        <v>0.095</v>
       </c>
       <c r="G31" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="H31" t="s">
         <v>56</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000153</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000022333358323258</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000818889805186127</v>
       </c>
       <c r="K31" t="s">
         <v>57</v>
@@ -5412,25 +5454,25 @@
         <v>363</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8919</v>
+        <v>0.7732</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2486</v>
+        <v>0.6828</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3567</v>
+        <v>-0.0904</v>
       </c>
       <c r="G32" t="n">
-        <v>2.27</v>
+        <v>0.81</v>
       </c>
       <c r="H32" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I32" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000125</v>
+        <v>0.00000000000000000000000000000000000000000113098465710804</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000133</v>
+        <v>0.00000000000000000000000000000000000000000124408312281885</v>
       </c>
       <c r="K32" t="s">
         <v>57</v>
@@ -5447,25 +5489,25 @@
         <v>363</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9624</v>
+        <v>-1.5061</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1328</v>
+        <v>-1.4378</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1704</v>
+        <v>0.0684</v>
       </c>
       <c r="G33" t="n">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000111</v>
+        <v>0.000000000000000000000000000000000000000000000000000000893758586834825</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000115</v>
+        <v>0.0000000000000000000000000000000000000000000000000000010170356332948</v>
       </c>
       <c r="K33" t="s">
         <v>57</v>
@@ -5482,25 +5524,25 @@
         <v>363</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.3677</v>
+        <v>-1.4063</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1858</v>
+        <v>-1.4593</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1819</v>
+        <v>-0.053</v>
       </c>
       <c r="G34" t="n">
-        <v>1.52</v>
+        <v>0.89</v>
       </c>
       <c r="H34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>0.000000000000000000000000000000000000000027</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000110225325889987</v>
       </c>
       <c r="J34" t="n">
-        <v>0.000000000000000000000000000000000000000027</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000139901375168061</v>
       </c>
       <c r="K34" t="s">
         <v>57</v>
